--- a/filer/45349918_ecco.xlsx
+++ b/filer/45349918_ecco.xlsx
@@ -5766,10 +5766,18 @@
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
+      <c r="B24" s="16" t="n">
+        <v>52972</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>75990</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>75043</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>82305</v>
+      </c>
       <c r="F24" s="16" t="n">
         <v>8480</v>
       </c>
@@ -7672,7 +7680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7748,29 +7756,23 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndAmortisationOfIntangibleAssets</t>
+          <t>fsa:AcquisitionOfOtherCompany</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndAmortisationOfIntangibleAssets</t>
+          <t>fsa:AcquisitionOfOtherCompany</t>
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>75063</v>
+        <v>125970</v>
       </c>
       <c r="E3" s="35" t="n">
-        <v>92547</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>139033</v>
-      </c>
-      <c r="G3" s="35" t="n">
-        <v>156249</v>
-      </c>
-      <c r="H3" s="35" t="n">
-        <v>178612</v>
-      </c>
+        <v>30586</v>
+      </c>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="35" t="n"/>
       <c r="I3" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7785,28 +7787,20 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
+          <t>fsa:AssetsHeldForSaleInventories</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:AccumulatedImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n">
-        <v>465891</v>
-      </c>
-      <c r="E4" s="38" t="n">
-        <v>487193</v>
-      </c>
-      <c r="F4" s="38" t="n">
-        <v>572243</v>
-      </c>
-      <c r="G4" s="38" t="n">
-        <v>557537</v>
-      </c>
+          <t>fsa:AssetsHeldForSaleInventories</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n"/>
+      <c r="E4" s="38" t="n"/>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
       <c r="H4" s="38" t="n">
-        <v>592690</v>
+        <v>486398</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7822,23 +7816,21 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:AcquisitionOfOtherCompany</t>
+          <t>fsa:CashCapitalIncrease</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:AcquisitionOfOtherCompany</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>125970</v>
-      </c>
-      <c r="E5" s="35" t="n">
-        <v>30586</v>
-      </c>
+          <t>fsa:CashCapitalIncrease</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n"/>
+      <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
       <c r="G5" s="35" t="n"/>
-      <c r="H5" s="35" t="n"/>
+      <c r="H5" s="35" t="n">
+        <v>2145</v>
+      </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7853,28 +7845,20 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssets</t>
+          <t>fsa:CashFlowsStatement</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n">
-        <v>118542</v>
-      </c>
-      <c r="E6" s="38" t="n">
-        <v>14681</v>
-      </c>
-      <c r="F6" s="38" t="n">
-        <v>18531</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>13833</v>
-      </c>
+          <t>fsa:CashFlowsStatement</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n"/>
+      <c r="E6" s="38" t="n"/>
+      <c r="F6" s="38" t="n"/>
+      <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n">
-        <v>13387</v>
+        <v>2</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7890,21 +7874,29 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssetsThroughMergersAndBusinessCombinations</t>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToIntangibleAssetsThroughMergersAndBusinessCombinations</t>
-        </is>
-      </c>
-      <c r="D7" s="35" t="n"/>
-      <c r="E7" s="35" t="n"/>
+          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>170</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>74</v>
+      </c>
       <c r="F7" s="35" t="n">
-        <v>5556</v>
-      </c>
-      <c r="G7" s="35" t="n"/>
-      <c r="H7" s="35" t="n"/>
+        <v>84</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>56</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>110</v>
+      </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7919,29 +7911,23 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipment</t>
+          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>61000</v>
-      </c>
+          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n"/>
       <c r="E8" s="38" t="n">
-        <v>47773</v>
+        <v>-32968</v>
       </c>
       <c r="F8" s="38" t="n">
-        <v>57844</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>36965</v>
-      </c>
-      <c r="H8" s="38" t="n">
-        <v>30327</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" s="38" t="n"/>
+      <c r="H8" s="38" t="n"/>
       <c r="I8" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7956,18 +7942,18 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipmentThroughMergersAndBusinessCombinations</t>
+          <t>fsa:InterestExpenseAssignedToAssociates</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>fsa:AdditionsToPropertyPlantAndEquipmentThroughMergersAndBusinessCombinations</t>
+          <t>fsa:InterestExpenseAssignedToAssociates</t>
         </is>
       </c>
       <c r="D9" s="35" t="n"/>
       <c r="E9" s="35" t="n"/>
       <c r="F9" s="35" t="n">
-        <v>54051</v>
+        <v>-529</v>
       </c>
       <c r="G9" s="35" t="n"/>
       <c r="H9" s="35" t="n"/>
@@ -7985,12 +7971,12 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>fsa:AssetsHeldForSaleInventories</t>
+          <t>fsa:InterestExpenseToParticipatingInterests</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>fsa:AssetsHeldForSaleInventories</t>
+          <t>fsa:InterestExpenseToParticipatingInterests</t>
         </is>
       </c>
       <c r="D10" s="38" t="n"/>
@@ -7998,7 +7984,7 @@
       <c r="F10" s="38" t="n"/>
       <c r="G10" s="38" t="n"/>
       <c r="H10" s="38" t="n">
-        <v>486398</v>
+        <v>-2891</v>
       </c>
       <c r="I10" s="39" t="inlineStr">
         <is>
@@ -8014,21 +8000,21 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>fsa:CashCapitalIncrease</t>
+          <t>fsa:InterestIncomeFromAssociates</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>fsa:CashCapitalIncrease</t>
+          <t>fsa:InterestIncomeFromAssociates</t>
         </is>
       </c>
       <c r="D11" s="35" t="n"/>
       <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
+      <c r="F11" s="35" t="n">
+        <v>13</v>
+      </c>
       <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n">
-        <v>2145</v>
-      </c>
+      <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8043,21 +8029,21 @@
       </c>
       <c r="B12" s="37" t="inlineStr">
         <is>
-          <t>fsa:CashFlowsStatement</t>
+          <t>fsa:InterestIncomeFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
         <is>
-          <t>fsa:CashFlowsStatement</t>
+          <t>fsa:InterestIncomeFromParticipatingInterests</t>
         </is>
       </c>
       <c r="D12" s="38" t="n"/>
       <c r="E12" s="38" t="n"/>
       <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n"/>
-      <c r="H12" s="38" t="n">
-        <v>2</v>
-      </c>
+      <c r="G12" s="38" t="n">
+        <v>-3160</v>
+      </c>
+      <c r="H12" s="38" t="n"/>
       <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8072,29 +8058,23 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
+          <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>1202</v>
-      </c>
+          <t>fsa:LongtermParticipatingInterests</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n"/>
       <c r="E13" s="35" t="n">
-        <v>689</v>
+        <v>32032</v>
       </c>
       <c r="F13" s="35" t="n">
-        <v>1488</v>
-      </c>
-      <c r="G13" s="35" t="n">
-        <v>6509</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <v>4589</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="35" t="n"/>
+      <c r="H13" s="35" t="n"/>
       <c r="I13" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8109,21 +8089,21 @@
       </c>
       <c r="B14" s="37" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfIntangibleAssetsByDivisionAndSaleOfOtherCompany</t>
+          <t>fsa:LongtermPayablesToParticipatingInterests</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfIntangibleAssetsByDivisionAndSaleOfOtherCompany</t>
+          <t>fsa:LongtermPayablesToParticipatingInterests</t>
         </is>
       </c>
       <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n">
-        <v>1259</v>
-      </c>
+      <c r="E14" s="38" t="n"/>
       <c r="F14" s="38" t="n"/>
       <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n"/>
+      <c r="H14" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="I14" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8138,29 +8118,23 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipment</t>
+          <t>fsa:LongtermReceivablesFromAssociates</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D15" s="35" t="n">
-        <v>15889</v>
-      </c>
+          <t>fsa:LongtermReceivablesFromAssociates</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n"/>
       <c r="E15" s="35" t="n">
-        <v>26612</v>
+        <v>24052</v>
       </c>
       <c r="F15" s="35" t="n">
-        <v>14268</v>
-      </c>
-      <c r="G15" s="35" t="n">
-        <v>49173</v>
-      </c>
-      <c r="H15" s="35" t="n">
-        <v>31561</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" s="35" t="n"/>
+      <c r="H15" s="35" t="n"/>
       <c r="I15" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8175,21 +8149,29 @@
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipmentByDivisionAndSaleOfOtherCompany</t>
+          <t>fsa:NumberOfEmployees</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>fsa:DisposalsOfPropertyPlantAndEquipmentByDivisionAndSaleOfOtherCompany</t>
-        </is>
-      </c>
-      <c r="D16" s="38" t="n"/>
+          <t>fsa:NumberOfEmployees</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="n">
+        <v>21</v>
+      </c>
       <c r="E16" s="38" t="n">
-        <v>22335</v>
-      </c>
-      <c r="F16" s="38" t="n"/>
-      <c r="G16" s="38" t="n"/>
-      <c r="H16" s="38" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="G16" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="H16" s="38" t="n">
+        <v>22</v>
+      </c>
       <c r="I16" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8204,29 +8186,21 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
+          <t>fsa:OtherShorttermDebtRaisedByIssuanceOfBonds</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>fsa:FeesForAuditorsPerformingOtherAssuranceReports</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>170</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>74</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>84</v>
-      </c>
+          <t>fsa:OtherShorttermDebtRaisedByIssuanceOfBonds</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n"/>
+      <c r="E17" s="35" t="n"/>
+      <c r="F17" s="35" t="n"/>
       <c r="G17" s="35" t="n">
-        <v>56</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <v>110</v>
-      </c>
+        <v>50000</v>
+      </c>
+      <c r="H17" s="35" t="n"/>
       <c r="I17" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8241,18 +8215,18 @@
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndAmortisationOfAdditionsToIntangibleAssetsThroughMergersAndBusinessCombinations</t>
+          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndAmortisationOfAdditionsToIntangibleAssetsThroughMergersAndBusinessCombinations</t>
+          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
         </is>
       </c>
       <c r="D18" s="38" t="n"/>
       <c r="E18" s="38" t="n"/>
       <c r="F18" s="38" t="n">
-        <v>3346</v>
+        <v>21922</v>
       </c>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
@@ -8270,25 +8244,23 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
+          <t>fsa:PurchaseOfMinorityShares</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D19" s="35" t="n"/>
+          <t>fsa:PurchaseOfMinorityShares</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>250</v>
+      </c>
       <c r="E19" s="35" t="n">
-        <v>-1289</v>
-      </c>
-      <c r="F19" s="35" t="n">
-        <v>-679</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F19" s="35" t="n"/>
       <c r="G19" s="35" t="n"/>
-      <c r="H19" s="35" t="n">
-        <v>-2772</v>
-      </c>
+      <c r="H19" s="35" t="n"/>
       <c r="I19" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8303,19 +8275,21 @@
       </c>
       <c r="B20" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationOfAdditionsToPropertyPlantAndEquipmentThroughMergersAndBusinessCombinations</t>
+          <t>fsa:SaleOfMinorityShares</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationOfAdditionsToPropertyPlantAndEquipmentThroughMergersAndBusinessCombinations</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="n"/>
-      <c r="E20" s="38" t="n"/>
-      <c r="F20" s="38" t="n">
-        <v>41204</v>
-      </c>
+          <t>fsa:SaleOfMinorityShares</t>
+        </is>
+      </c>
+      <c r="D20" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="38" t="n"/>
       <c r="G20" s="38" t="n"/>
       <c r="H20" s="38" t="n"/>
       <c r="I20" s="39" t="inlineStr">
@@ -8332,24 +8306,20 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
+          <t>fsa:SalesOfTreasuryShares</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
+          <t>fsa:SalesOfTreasuryShares</t>
         </is>
       </c>
       <c r="D21" s="35" t="n"/>
       <c r="E21" s="35" t="n"/>
-      <c r="F21" s="35" t="n">
-        <v>-13859</v>
-      </c>
-      <c r="G21" s="35" t="n">
-        <v>-42071</v>
-      </c>
+      <c r="F21" s="35" t="n"/>
+      <c r="G21" s="35" t="n"/>
       <c r="H21" s="35" t="n">
-        <v>-27995</v>
+        <v>-205</v>
       </c>
       <c r="I21" s="36" t="inlineStr">
         <is>
@@ -8365,22 +8335,26 @@
       </c>
       <c r="B22" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationsOfDisposalsOfIntangibleAssetsOnDemergerAndSaleOfOtherEnterprise</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationsOfDisposalsOfIntangibleAssetsOnDemergerAndSaleOfOtherEnterprise</t>
+          <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
       <c r="D22" s="38" t="n">
-        <v>92547</v>
+        <v>52238</v>
       </c>
       <c r="E22" s="38" t="n">
-        <v>113242</v>
-      </c>
-      <c r="F22" s="38" t="n"/>
-      <c r="G22" s="38" t="n"/>
+        <v>76515</v>
+      </c>
+      <c r="F22" s="38" t="n">
+        <v>31679</v>
+      </c>
+      <c r="G22" s="38" t="n">
+        <v>16887</v>
+      </c>
       <c r="H22" s="38" t="n"/>
       <c r="I22" s="39" t="inlineStr">
         <is>
@@ -8396,21 +8370,21 @@
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationsOfDisposalsOfPropertyPlantAndEquipmentByDivisionAndSaleOfOtherCompany</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>fsa:ImpairmentLossesAndDepreciationsOfDisposalsOfPropertyPlantAndEquipmentByDivisionAndSaleOfOtherCompany</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n">
-        <v>21107</v>
-      </c>
+      <c r="E23" s="35" t="n"/>
       <c r="F23" s="35" t="n"/>
       <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
+      <c r="H23" s="35" t="n">
+        <v>15353</v>
+      </c>
       <c r="I23" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8425,23 +8399,21 @@
       </c>
       <c r="B24" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
+          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
         </is>
       </c>
       <c r="D24" s="38" t="n"/>
-      <c r="E24" s="38" t="n">
-        <v>-32968</v>
-      </c>
-      <c r="F24" s="38" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" s="38" t="n"/>
+      <c r="F24" s="38" t="n"/>
       <c r="G24" s="38" t="n"/>
-      <c r="H24" s="38" t="n"/>
+      <c r="H24" s="38" t="n">
+        <v>195</v>
+      </c>
       <c r="I24" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8456,28 +8428,20 @@
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndAmortisationOfIntangibleAssetsThroughNetExchangeDifferences</t>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndAmortisationOfIntangibleAssetsThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>-1482</v>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>926</v>
-      </c>
-      <c r="F25" s="35" t="n">
-        <v>566</v>
-      </c>
-      <c r="G25" s="35" t="n">
-        <v>-1540</v>
-      </c>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="n"/>
+      <c r="E25" s="35" t="n"/>
+      <c r="F25" s="35" t="n"/>
+      <c r="G25" s="35" t="n"/>
       <c r="H25" s="35" t="n">
-        <v>687</v>
+        <v>-16560</v>
       </c>
       <c r="I25" s="36" t="inlineStr">
         <is>
@@ -8493,1064 +8457,22 @@
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndDepreciationOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
+          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>fsa:IncreaseDecreaseOfImpairmentLossesAndDepreciationOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D26" s="38" t="n">
-        <v>-20606</v>
-      </c>
-      <c r="E26" s="38" t="n">
-        <v>16533</v>
-      </c>
-      <c r="F26" s="38" t="n">
-        <v>156</v>
-      </c>
+          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="n"/>
+      <c r="E26" s="38" t="n"/>
+      <c r="F26" s="38" t="n"/>
       <c r="G26" s="38" t="n">
-        <v>-25124</v>
-      </c>
-      <c r="H26" s="38" t="n">
-        <v>12655</v>
-      </c>
+        <v>66779</v>
+      </c>
+      <c r="H26" s="38" t="n"/>
       <c r="I26" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>-567</v>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>1371</v>
-      </c>
-      <c r="F27" s="35" t="n">
-        <v>226</v>
-      </c>
-      <c r="G27" s="35" t="n">
-        <v>-2285</v>
-      </c>
-      <c r="H27" s="35" t="n">
-        <v>666</v>
-      </c>
-      <c r="I27" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B28" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughTransfers</t>
-        </is>
-      </c>
-      <c r="C28" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfIntangibleAssetsThroughTransfers</t>
-        </is>
-      </c>
-      <c r="D28" s="38" t="n">
-        <v>-829</v>
-      </c>
-      <c r="E28" s="38" t="n">
-        <v>376</v>
-      </c>
-      <c r="F28" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B29" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
-        </is>
-      </c>
-      <c r="C29" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfInvestmentsThroughNetExchangeDifferencesEquity</t>
-        </is>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>-42642</v>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>49847</v>
-      </c>
-      <c r="F29" s="35" t="n">
-        <v>6173</v>
-      </c>
-      <c r="G29" s="35" t="n">
-        <v>66186</v>
-      </c>
-      <c r="H29" s="35" t="n">
-        <v>-22252</v>
-      </c>
-      <c r="I29" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="C30" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughNetExchangeDifferences</t>
-        </is>
-      </c>
-      <c r="D30" s="38" t="n">
-        <v>-31313</v>
-      </c>
-      <c r="E30" s="38" t="n">
-        <v>29057</v>
-      </c>
-      <c r="F30" s="38" t="n">
-        <v>-915</v>
-      </c>
-      <c r="G30" s="38" t="n">
-        <v>-30021</v>
-      </c>
-      <c r="H30" s="38" t="n">
-        <v>17509</v>
-      </c>
-      <c r="I30" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B31" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughTransfers</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>fsa:IncreaseDecreaseOfPropertyPlantAndEquipmentThroughTransfers</t>
-        </is>
-      </c>
-      <c r="D31" s="35" t="n">
-        <v>829</v>
-      </c>
-      <c r="E31" s="35" t="n">
-        <v>-376</v>
-      </c>
-      <c r="F31" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B32" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IntangibleAssetsGross</t>
-        </is>
-      </c>
-      <c r="C32" s="37" t="inlineStr">
-        <is>
-          <t>fsa:IntangibleAssetsGross</t>
-        </is>
-      </c>
-      <c r="D32" s="38" t="n">
-        <v>218178</v>
-      </c>
-      <c r="E32" s="38" t="n">
-        <v>232658</v>
-      </c>
-      <c r="F32" s="38" t="n">
-        <v>255483</v>
-      </c>
-      <c r="G32" s="38" t="n">
-        <v>260522</v>
-      </c>
-      <c r="H32" s="38" t="n">
-        <v>269986</v>
-      </c>
-      <c r="I32" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>fsa:InterestExpenseAssignedToAssociates</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="inlineStr">
-        <is>
-          <t>fsa:InterestExpenseAssignedToAssociates</t>
-        </is>
-      </c>
-      <c r="D33" s="35" t="n"/>
-      <c r="E33" s="35" t="n"/>
-      <c r="F33" s="35" t="n">
-        <v>-529</v>
-      </c>
-      <c r="G33" s="35" t="n"/>
-      <c r="H33" s="35" t="n"/>
-      <c r="I33" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B34" s="37" t="inlineStr">
-        <is>
-          <t>fsa:InterestExpenseToParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C34" s="37" t="inlineStr">
-        <is>
-          <t>fsa:InterestExpenseToParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="n"/>
-      <c r="H34" s="38" t="n">
-        <v>-2891</v>
-      </c>
-      <c r="I34" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B35" s="34" t="inlineStr">
-        <is>
-          <t>fsa:InterestIncomeFromAssociates</t>
-        </is>
-      </c>
-      <c r="C35" s="34" t="inlineStr">
-        <is>
-          <t>fsa:InterestIncomeFromAssociates</t>
-        </is>
-      </c>
-      <c r="D35" s="35" t="n"/>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="35" t="n">
-        <v>13</v>
-      </c>
-      <c r="G35" s="35" t="n"/>
-      <c r="H35" s="35" t="n"/>
-      <c r="I35" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B36" s="37" t="inlineStr">
-        <is>
-          <t>fsa:InterestIncomeFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C36" s="37" t="inlineStr">
-        <is>
-          <t>fsa:InterestIncomeFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D36" s="38" t="n"/>
-      <c r="E36" s="38" t="n"/>
-      <c r="F36" s="38" t="n"/>
-      <c r="G36" s="38" t="n">
-        <v>-3160</v>
-      </c>
-      <c r="H36" s="38" t="n"/>
-      <c r="I36" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B37" s="34" t="inlineStr">
-        <is>
-          <t>fsa:LongtermParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C37" s="34" t="inlineStr">
-        <is>
-          <t>fsa:LongtermParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D37" s="35" t="n"/>
-      <c r="E37" s="35" t="n">
-        <v>32032</v>
-      </c>
-      <c r="F37" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="35" t="n"/>
-      <c r="H37" s="35" t="n"/>
-      <c r="I37" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>fsa:LongtermPayablesToParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C38" s="37" t="inlineStr">
-        <is>
-          <t>fsa:LongtermPayablesToParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D38" s="38" t="n"/>
-      <c r="E38" s="38" t="n"/>
-      <c r="F38" s="38" t="n"/>
-      <c r="G38" s="38" t="n"/>
-      <c r="H38" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B39" s="34" t="inlineStr">
-        <is>
-          <t>fsa:LongtermReceivablesFromAssociates</t>
-        </is>
-      </c>
-      <c r="C39" s="34" t="inlineStr">
-        <is>
-          <t>fsa:LongtermReceivablesFromAssociates</t>
-        </is>
-      </c>
-      <c r="D39" s="35" t="n"/>
-      <c r="E39" s="35" t="n">
-        <v>24052</v>
-      </c>
-      <c r="F39" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="35" t="n"/>
-      <c r="H39" s="35" t="n"/>
-      <c r="I39" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B40" s="37" t="inlineStr">
-        <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
-        </is>
-      </c>
-      <c r="C40" s="37" t="inlineStr">
-        <is>
-          <t>fsa:NoncurrentDeferredTaxAssets</t>
-        </is>
-      </c>
-      <c r="D40" s="38" t="n">
-        <v>52972</v>
-      </c>
-      <c r="E40" s="38" t="n">
-        <v>75990</v>
-      </c>
-      <c r="F40" s="38" t="n">
-        <v>75043</v>
-      </c>
-      <c r="G40" s="38" t="n">
-        <v>82305</v>
-      </c>
-      <c r="H40" s="38" t="n">
-        <v>89500</v>
-      </c>
-      <c r="I40" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B41" s="34" t="inlineStr">
-        <is>
-          <t>fsa:NumberOfEmployees</t>
-        </is>
-      </c>
-      <c r="C41" s="34" t="inlineStr">
-        <is>
-          <t>fsa:NumberOfEmployees</t>
-        </is>
-      </c>
-      <c r="D41" s="35" t="n">
-        <v>21</v>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>22</v>
-      </c>
-      <c r="F41" s="35" t="n">
-        <v>24</v>
-      </c>
-      <c r="G41" s="35" t="n">
-        <v>23</v>
-      </c>
-      <c r="H41" s="35" t="n">
-        <v>22</v>
-      </c>
-      <c r="I41" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B42" s="37" t="inlineStr">
-        <is>
-          <t>fsa:OtherShorttermDebtRaisedByIssuanceOfBonds</t>
-        </is>
-      </c>
-      <c r="C42" s="37" t="inlineStr">
-        <is>
-          <t>fsa:OtherShorttermDebtRaisedByIssuanceOfBonds</t>
-        </is>
-      </c>
-      <c r="D42" s="38" t="n"/>
-      <c r="E42" s="38" t="n"/>
-      <c r="F42" s="38" t="n"/>
-      <c r="G42" s="38" t="n">
-        <v>50000</v>
-      </c>
-      <c r="H42" s="38" t="n"/>
-      <c r="I42" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B43" s="34" t="inlineStr">
-        <is>
-          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
-        </is>
-      </c>
-      <c r="C43" s="34" t="inlineStr">
-        <is>
-          <t>fsa:PensionsAndSimilarLiabilitiesLiabilitiesLongterm</t>
-        </is>
-      </c>
-      <c r="D43" s="35" t="n"/>
-      <c r="E43" s="35" t="n"/>
-      <c r="F43" s="35" t="n">
-        <v>21922</v>
-      </c>
-      <c r="G43" s="35" t="n"/>
-      <c r="H43" s="35" t="n"/>
-      <c r="I43" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B44" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ProfitLossAfterAttributableToMinorityInterest</t>
-        </is>
-      </c>
-      <c r="C44" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ProfitLossAfterAttributableToMinorityInterest</t>
-        </is>
-      </c>
-      <c r="D44" s="38" t="n">
-        <v>-6413</v>
-      </c>
-      <c r="E44" s="38" t="n">
-        <v>-23954</v>
-      </c>
-      <c r="F44" s="38" t="n">
-        <v>39652</v>
-      </c>
-      <c r="G44" s="38" t="n">
-        <v>47035</v>
-      </c>
-      <c r="H44" s="38" t="n"/>
-      <c r="I44" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B45" s="34" t="inlineStr">
-        <is>
-          <t>fsa:PropertyPlantAndEquipmentGross</t>
-        </is>
-      </c>
-      <c r="C45" s="34" t="inlineStr">
-        <is>
-          <t>fsa:PropertyPlantAndEquipmentGross</t>
-        </is>
-      </c>
-      <c r="D45" s="35" t="n">
-        <v>740854</v>
-      </c>
-      <c r="E45" s="35" t="n">
-        <v>768361</v>
-      </c>
-      <c r="F45" s="35" t="n">
-        <v>865073</v>
-      </c>
-      <c r="G45" s="35" t="n">
-        <v>822844</v>
-      </c>
-      <c r="H45" s="35" t="n">
-        <v>839119</v>
-      </c>
-      <c r="I45" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B46" s="37" t="inlineStr">
-        <is>
-          <t>fsa:PurchaseOfMinorityShares</t>
-        </is>
-      </c>
-      <c r="C46" s="37" t="inlineStr">
-        <is>
-          <t>fsa:PurchaseOfMinorityShares</t>
-        </is>
-      </c>
-      <c r="D46" s="38" t="n">
-        <v>250</v>
-      </c>
-      <c r="E46" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="38" t="n"/>
-      <c r="G46" s="38" t="n"/>
-      <c r="H46" s="38" t="n"/>
-      <c r="I46" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B47" s="34" t="inlineStr">
-        <is>
-          <t>fsa:RevaluationsOfActuarialProfitLossForReportingPeriod</t>
-        </is>
-      </c>
-      <c r="C47" s="34" t="inlineStr">
-        <is>
-          <t>fsa:RevaluationsOfActuarialProfitLossForReportingPeriod</t>
-        </is>
-      </c>
-      <c r="D47" s="35" t="n"/>
-      <c r="E47" s="35" t="n"/>
-      <c r="F47" s="35" t="n"/>
-      <c r="G47" s="35" t="n">
-        <v>-489</v>
-      </c>
-      <c r="H47" s="35" t="n"/>
-      <c r="I47" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B48" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C48" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndAmortisationOfDisposedIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D48" s="38" t="n">
-        <v>366</v>
-      </c>
-      <c r="E48" s="38" t="n">
-        <v>929</v>
-      </c>
-      <c r="F48" s="38" t="n">
-        <v>1237</v>
-      </c>
-      <c r="G48" s="38" t="n">
-        <v>6091</v>
-      </c>
-      <c r="H48" s="38" t="n"/>
-      <c r="I48" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B49" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C49" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ReversalsOfImpairmentLossesAndDepreciationOfDisposedPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D49" s="35" t="n">
-        <v>13346</v>
-      </c>
-      <c r="E49" s="35" t="n">
-        <v>23167</v>
-      </c>
-      <c r="F49" s="35" t="n">
-        <v>1886</v>
-      </c>
-      <c r="G49" s="35" t="n">
-        <v>4096</v>
-      </c>
-      <c r="H49" s="35" t="n"/>
-      <c r="I49" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B50" s="37" t="inlineStr">
-        <is>
-          <t>fsa:SaleOfMinorityShares</t>
-        </is>
-      </c>
-      <c r="C50" s="37" t="inlineStr">
-        <is>
-          <t>fsa:SaleOfMinorityShares</t>
-        </is>
-      </c>
-      <c r="D50" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="38" t="n"/>
-      <c r="G50" s="38" t="n"/>
-      <c r="H50" s="38" t="n"/>
-      <c r="I50" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B51" s="34" t="inlineStr">
-        <is>
-          <t>fsa:SalesOfTreasuryShares</t>
-        </is>
-      </c>
-      <c r="C51" s="34" t="inlineStr">
-        <is>
-          <t>fsa:SalesOfTreasuryShares</t>
-        </is>
-      </c>
-      <c r="D51" s="35" t="n"/>
-      <c r="E51" s="35" t="n"/>
-      <c r="F51" s="35" t="n"/>
-      <c r="G51" s="35" t="n"/>
-      <c r="H51" s="35" t="n">
-        <v>-205</v>
-      </c>
-      <c r="I51" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B52" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
-        </is>
-      </c>
-      <c r="C52" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToAssociates</t>
-        </is>
-      </c>
-      <c r="D52" s="38" t="n">
-        <v>52238</v>
-      </c>
-      <c r="E52" s="38" t="n">
-        <v>76515</v>
-      </c>
-      <c r="F52" s="38" t="n">
-        <v>31679</v>
-      </c>
-      <c r="G52" s="38" t="n">
-        <v>16887</v>
-      </c>
-      <c r="H52" s="38" t="n"/>
-      <c r="I52" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B53" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
-        </is>
-      </c>
-      <c r="C53" s="34" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
-        </is>
-      </c>
-      <c r="D53" s="35" t="n"/>
-      <c r="E53" s="35" t="n"/>
-      <c r="F53" s="35" t="n"/>
-      <c r="G53" s="35" t="n"/>
-      <c r="H53" s="35" t="n">
-        <v>15353</v>
-      </c>
-      <c r="I53" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B54" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="C54" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermReceivablesFromParticipatingInterests</t>
-        </is>
-      </c>
-      <c r="D54" s="38" t="n"/>
-      <c r="E54" s="38" t="n"/>
-      <c r="F54" s="38" t="n"/>
-      <c r="G54" s="38" t="n"/>
-      <c r="H54" s="38" t="n">
-        <v>195</v>
-      </c>
-      <c r="I54" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B55" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferImpairmentLossesAndAmortisationOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="C55" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferImpairmentLossesAndAmortisationOfIntangibleAssets</t>
-        </is>
-      </c>
-      <c r="D55" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="35" t="n"/>
-      <c r="F55" s="35" t="n"/>
-      <c r="G55" s="35" t="n"/>
-      <c r="H55" s="35" t="n"/>
-      <c r="I55" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B56" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TransferImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="C56" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TransferImpairmentLossesAndDepreciationOfPropertyPlantAndEquipment</t>
-        </is>
-      </c>
-      <c r="D56" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="38" t="n"/>
-      <c r="G56" s="38" t="n"/>
-      <c r="H56" s="38" t="n"/>
-      <c r="I56" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B57" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
-        </is>
-      </c>
-      <c r="C57" s="34" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
-        </is>
-      </c>
-      <c r="D57" s="35" t="n"/>
-      <c r="E57" s="35" t="n"/>
-      <c r="F57" s="35" t="n"/>
-      <c r="G57" s="35" t="n"/>
-      <c r="H57" s="35" t="n">
-        <v>-16560</v>
-      </c>
-      <c r="I57" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B58" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
-        </is>
-      </c>
-      <c r="C58" s="37" t="inlineStr">
-        <is>
-          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
-        </is>
-      </c>
-      <c r="D58" s="38" t="n"/>
-      <c r="E58" s="38" t="n"/>
-      <c r="F58" s="38" t="n"/>
-      <c r="G58" s="38" t="n">
-        <v>66779</v>
-      </c>
-      <c r="H58" s="38" t="n"/>
-      <c r="I58" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/45349918_ecco.xlsx
+++ b/filer/45349918_ecco.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse t.kr.</t>
+          <t>Resultatopgørelse t.EUR</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -1527,7 +1527,7 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>AKTIVER t.kr.</t>
+          <t>AKTIVER t.EUR</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
@@ -3005,7 +3005,7 @@
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>PASSIVER t.kr.</t>
+          <t>PASSIVER t.EUR</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
@@ -4846,7 +4846,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Resultatopgørelse &amp; nøgleoplysninger (t.kr.)</t>
+          <t>Resultatopgørelse &amp; nøgleoplysninger (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -5271,7 +5271,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Balance (t.kr.)</t>
+          <t>Balance (t.EUR)</t>
         </is>
       </c>
       <c r="B1" s="3" t="n">
@@ -7529,15 +7529,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_45349918'!$F$31="","—",IF(ABS(B21-'balance_raw_45349918'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_45349918'!$F$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_45349918'!$F$31="","—",IF(ABS(B21-'balance_raw_45349918'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_45349918'!$F$31,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_45349918'!$E$31="","—",IF(ABS(C21-'balance_raw_45349918'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_45349918'!$E$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_45349918'!$E$31="","—",IF(ABS(C21-'balance_raw_45349918'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_45349918'!$E$31,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_45349918'!$D$31="","—",IF(ABS(D21-'balance_raw_45349918'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_45349918'!$D$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_45349918'!$D$31="","—",IF(ABS(D21-'balance_raw_45349918'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_45349918'!$D$31,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -7553,15 +7553,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_45349918'!$F$59="","—",IF(ABS(B25-'balance_raw_45349918'!$F$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_45349918'!$F$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_45349918'!$F$59="","—",IF(ABS(B25-'balance_raw_45349918'!$F$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_45349918'!$F$59,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_45349918'!$E$59="","—",IF(ABS(C25-'balance_raw_45349918'!$E$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_45349918'!$E$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_45349918'!$E$59="","—",IF(ABS(C25-'balance_raw_45349918'!$E$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_45349918'!$E$59,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_45349918'!$D$59="","—",IF(ABS(D25-'balance_raw_45349918'!$D$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_45349918'!$D$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_45349918'!$D$59="","—",IF(ABS(D25-'balance_raw_45349918'!$D$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_45349918'!$D$59,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7577,15 +7577,15 @@
         </is>
       </c>
       <c r="B63" s="29">
-        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(B21-B25)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-B25,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="C63" s="29">
-        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(C21-C25)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-C25,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="D63" s="29">
-        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" t.kr.")</f>
+        <f>IF(ABS(D21-D25)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-D25,"+#,##0;-#,##0")&amp;" t.EUR")</f>
         <v/>
       </c>
       <c r="F63" s="25" t="inlineStr">
@@ -7601,15 +7601,15 @@
         </is>
       </c>
       <c r="B64" s="29">
-        <f>IF('res_raw_45349918'!$F$6="","—",IF(ABS(B9-'res_raw_45349918'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw_45349918'!$F$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$F$6="","—",IF(ABS(B9-'res_raw_45349918'!$F$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(B9-'res_raw_45349918'!$F$6,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C64" s="29">
-        <f>IF('res_raw_45349918'!$E$6="","—",IF(ABS(C9-'res_raw_45349918'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw_45349918'!$E$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$E$6="","—",IF(ABS(C9-'res_raw_45349918'!$E$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(C9-'res_raw_45349918'!$E$6,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D64" s="29">
-        <f>IF('res_raw_45349918'!$D$6="","—",IF(ABS(D9-'res_raw_45349918'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw_45349918'!$D$6,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$D$6="","—",IF(ABS(D9-'res_raw_45349918'!$D$6)&lt;=1,"✓ OK","❌ "&amp;TEXT(D9-'res_raw_45349918'!$D$6,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F64" s="25" t="inlineStr">
@@ -7625,15 +7625,15 @@
         </is>
       </c>
       <c r="B65" s="29">
-        <f>IF('res_raw_45349918'!$F$11="","—",IF(ABS(B13-'res_raw_45349918'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_45349918'!$F$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$F$11="","—",IF(ABS(B13-'res_raw_45349918'!$F$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(B13-'res_raw_45349918'!$F$11,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C65" s="29">
-        <f>IF('res_raw_45349918'!$E$11="","—",IF(ABS(C13-'res_raw_45349918'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_45349918'!$E$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$E$11="","—",IF(ABS(C13-'res_raw_45349918'!$E$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(C13-'res_raw_45349918'!$E$11,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D65" s="29">
-        <f>IF('res_raw_45349918'!$D$11="","—",IF(ABS(D13-'res_raw_45349918'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_45349918'!$D$11,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$D$11="","—",IF(ABS(D13-'res_raw_45349918'!$D$11)&lt;=1,"✓ OK","❌ "&amp;TEXT(D13-'res_raw_45349918'!$D$11,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F65" s="25" t="inlineStr">
@@ -7649,15 +7649,15 @@
         </is>
       </c>
       <c r="B66" s="29">
-        <f>IF('res_raw_45349918'!$F$16="","—",IF(ABS(B16-'res_raw_45349918'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_45349918'!$F$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$F$16="","—",IF(ABS(B16-'res_raw_45349918'!$F$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(B16-'res_raw_45349918'!$F$16,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="C66" s="29">
-        <f>IF('res_raw_45349918'!$E$16="","—",IF(ABS(C16-'res_raw_45349918'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_45349918'!$E$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$E$16="","—",IF(ABS(C16-'res_raw_45349918'!$E$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(C16-'res_raw_45349918'!$E$16,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="D66" s="29">
-        <f>IF('res_raw_45349918'!$D$16="","—",IF(ABS(D16-'res_raw_45349918'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_45349918'!$D$16,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('res_raw_45349918'!$D$16="","—",IF(ABS(D16-'res_raw_45349918'!$D$16)&lt;=1,"✓ OK","❌ "&amp;TEXT(D16-'res_raw_45349918'!$D$16,"+#,##0;-#,##0")&amp;" t.EUR"))</f>
         <v/>
       </c>
       <c r="F66" s="25" t="inlineStr">

--- a/filer/45349918_ecco.xlsx
+++ b/filer/45349918_ecco.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/45349918_ecco.xlsx
+++ b/filer/45349918_ecco.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_45349918" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_45349918" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_45349918" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_45349918" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -648,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR) · Klasse C-stor · Revision</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.EUR) · Klasse C-stor · Independent Auditor’s Report</t>
         </is>
       </c>
     </row>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -3009,35 +3010,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4391,19 +4392,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4509,19 +4510,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -4818,6 +4819,148 @@
       </c>
       <c r="F99" s="13">
         <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_45349918'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_45349918'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_45349918'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_45349918'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_45349918'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_45349918'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_45349918'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_45349918'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_45349918'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_45349918'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B104" s="17">
+        <f>'pengestrom_raw_45349918'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C104" s="17">
+        <f>'pengestrom_raw_45349918'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D104" s="17">
+        <f>'pengestrom_raw_45349918'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E104" s="17">
+        <f>'pengestrom_raw_45349918'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F104" s="17">
+        <f>'pengestrom_raw_45349918'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B105" s="17">
+        <f>'pengestrom_raw_45349918'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C105" s="17">
+        <f>'pengestrom_raw_45349918'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D105" s="17">
+        <f>'pengestrom_raw_45349918'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E105" s="17">
+        <f>'pengestrom_raw_45349918'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F105" s="17">
+        <f>'pengestrom_raw_45349918'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B106">
+        <f>IF(ABS(('pengestrom_raw_45349918'!$B$2+'pengestrom_raw_45349918'!$B$3+'pengestrom_raw_45349918'!$B$4)-'pengestrom_raw_45349918'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_45349918'!$B$2+'pengestrom_raw_45349918'!$B$3+'pengestrom_raw_45349918'!$B$4)-'pengestrom_raw_45349918'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>IF(ABS(('pengestrom_raw_45349918'!$C$2+'pengestrom_raw_45349918'!$C$3+'pengestrom_raw_45349918'!$C$4)-'pengestrom_raw_45349918'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_45349918'!$C$2+'pengestrom_raw_45349918'!$C$3+'pengestrom_raw_45349918'!$C$4)-'pengestrom_raw_45349918'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>IF(ABS(('pengestrom_raw_45349918'!$D$2+'pengestrom_raw_45349918'!$D$3+'pengestrom_raw_45349918'!$D$4)-'pengestrom_raw_45349918'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_45349918'!$D$2+'pengestrom_raw_45349918'!$D$3+'pengestrom_raw_45349918'!$D$4)-'pengestrom_raw_45349918'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>IF(ABS(('pengestrom_raw_45349918'!$E$2+'pengestrom_raw_45349918'!$E$3+'pengestrom_raw_45349918'!$E$4)-'pengestrom_raw_45349918'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_45349918'!$E$2+'pengestrom_raw_45349918'!$E$3+'pengestrom_raw_45349918'!$E$4)-'pengestrom_raw_45349918'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>IF(ABS(('pengestrom_raw_45349918'!$F$2+'pengestrom_raw_45349918'!$F$3+'pengestrom_raw_45349918'!$F$4)-'pengestrom_raw_45349918'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_45349918'!$F$2+'pengestrom_raw_45349918'!$F$3+'pengestrom_raw_45349918'!$F$4)-'pengestrom_raw_45349918'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4850,401 +4993,397 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>1092470</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1218078</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1585780</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1570524</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1486978</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>1409831</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>12283</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>10424</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>3362</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>6203</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>9622</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>59346</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>-46135</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>-18896</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>-62382</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>6004</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>481757</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>430877</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>262616</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>286872</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>408049</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>436578</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>469228</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>450334</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>368736</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>365221</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>489059</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>492537</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>481831</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>477623</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>68950</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>71030</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>80665</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>77336</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>74941</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>65404</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>50242</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>84126</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>92520</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>114184</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>30157</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>44042</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>3291</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>6788</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>12587</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>17622</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>5281</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>4246</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>8797</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>15114</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>16918</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>65932</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>30333</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>23509</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>-5506</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>-8326</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-4331</v>
       </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n">
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n">
         <v>-25052</v>
       </c>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>44735</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>42832</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>88189</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>90029</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>5105</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>24779</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>21588</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>29356</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>39492</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>42994</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>42695</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>48787</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>23147</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>13476</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>48697</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>47035</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>-37590</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>-24008</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>22495</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>21613</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>23918</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>23188</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>21815</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>21075</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>-55156</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>-44328</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>-57435</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>-29863</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>-30327</v>
       </c>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5275,1175 +5414,1167 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>37</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>17401</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>1662</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>2105</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>2210</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>2170</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>2574</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>2538</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>97052</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>87765</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>78428</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>66467</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>55318</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>43829</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>125631</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>119416</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>116450</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>104273</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>91374</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>72705</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>147659</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>164123</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>177836</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>172671</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>169315</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>148106</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>47603</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>43751</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>40238</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>35368</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>28152</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>17731</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>39837</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>41142</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>42110</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>37928</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>34140</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>27722</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>39864</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>32152</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>32646</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>19340</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>14822</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>15498</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>274963</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>281168</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>292830</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>265307</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>246429</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>209057</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
+        <v>11808</v>
+      </c>
+      <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
-        <v>11808</v>
-      </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>63204</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>142257</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>88326</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>94113</v>
       </c>
-      <c r="F14" s="16" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>463798</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>542841</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>497606</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>463693</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>439021</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>369265</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>66121</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>67281</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>94688</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>75374</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>75394</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>57373</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>4997</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>5953</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>7519</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>5686</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>7316</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>4321</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>303806</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>320198</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>451088</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>445084</v>
       </c>
-      <c r="F18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>374924</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>393432</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>553295</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>526144</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>569108</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>547196</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>105228</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>85485</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>130513</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>101704</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>97091</v>
       </c>
+      <c r="F20" s="17" t="n">
+        <v>98569</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
-        <v>51580</v>
-      </c>
-      <c r="C22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>41348</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>45799</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>53202</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>44629</v>
       </c>
+      <c r="F22" s="17" t="n">
+        <v>37162</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>13013</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>26272</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>26253</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>29398</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>23698</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>29645</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>52972</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>75990</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>75043</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>82305</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>8480</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>16853</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>16978</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>15177</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>21000</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>6396</v>
       </c>
-      <c r="F26" s="16" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>243106</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>185243</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>223615</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>191333</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>174093</v>
       </c>
+      <c r="F27" s="17" t="n">
+        <v>182885</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="C28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>66</v>
       </c>
+      <c r="F28" s="17" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>238905</v>
-      </c>
-      <c r="C29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>297565</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>300253</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>298778</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>309184</v>
       </c>
+      <c r="F29" s="17" t="n">
+        <v>272957</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
-        <v>856958</v>
-      </c>
-      <c r="C30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>876243</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>1077193</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>1016283</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>1052451</v>
       </c>
+      <c r="F30" s="17" t="n">
+        <v>1003078</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>1320756</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>1419084</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>1574799</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>1479976</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>1491472</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>1372343</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n">
+      <c r="B32" s="17" t="n">
         <v>666</v>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="17" t="n">
         <v>666</v>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="17" t="n">
         <v>666</v>
       </c>
-      <c r="E32" s="16" t="n">
-        <v>666</v>
-      </c>
-      <c r="F32" s="16" t="n">
+      <c r="E32" s="17" t="n">
         <v>741</v>
       </c>
+      <c r="F32" s="17" t="n">
+        <v>741</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>1127</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>-11314</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>-2836</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>4863</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>3891</v>
       </c>
+      <c r="F35" s="17" t="n">
+        <v>-420</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>-37198</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>-4086</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>-7458</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>-55710</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>-39712</v>
       </c>
+      <c r="F36" s="17" t="n">
+        <v>-64615</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
-        <v>535282</v>
-      </c>
-      <c r="C37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>488170</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>475746</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>476623</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>481532</v>
       </c>
+      <c r="F37" s="17" t="n">
+        <v>448558</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>686787</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>678170</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>879426</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>843334</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>640688</v>
       </c>
+      <c r="F38" s="17" t="n">
+        <v>563843</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v>8509</v>
-      </c>
-      <c r="C39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>7166</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>9865</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>5461</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>1613</v>
       </c>
+      <c r="F39" s="17" t="n">
+        <v>6513</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>30872</v>
-      </c>
-      <c r="C40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>28913</v>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="C40" s="17" t="n">
         <v>6555</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="D40" s="17" t="n">
         <v>23368</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="E40" s="17" t="n">
         <v>25987</v>
       </c>
+      <c r="F40" s="17" t="n">
+        <v>26565</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>201193</v>
-      </c>
-      <c r="C42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>182155</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>375550</v>
       </c>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n">
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n">
         <v>361512</v>
       </c>
+      <c r="F42" s="17" t="n">
+        <v>394623</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>3434</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>50000</v>
       </c>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n">
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n">
         <v>395703</v>
       </c>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C47" s="16" t="n">
+      <c r="B47" s="17" t="n">
         <v>110843</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="C47" s="17" t="n">
         <v>84112</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <v>41841</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>144696</v>
       </c>
+      <c r="F47" s="17" t="n">
+        <v>94891</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C48" s="16" t="n">
+      <c r="B48" s="17" t="n">
         <v>90278</v>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="C48" s="17" t="n">
         <v>37809</v>
       </c>
-      <c r="E48" s="16" t="n">
+      <c r="D48" s="17" t="n">
         <v>438450</v>
       </c>
-      <c r="F48" s="16" t="n">
+      <c r="E48" s="17" t="n">
         <v>27593</v>
       </c>
+      <c r="F48" s="17" t="n">
+        <v>15270</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
-        <v>54952</v>
-      </c>
-      <c r="C50" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>73616</v>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>60037</v>
       </c>
-      <c r="E50" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>48747</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>74340</v>
       </c>
+      <c r="F50" s="17" t="n">
+        <v>75459</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C51" s="16" t="n">
+      <c r="C51" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F51" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>3495</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>15883</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>10628</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>11805</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>11853</v>
       </c>
+      <c r="F53" s="17" t="n">
+        <v>8904</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
-        <v>139927</v>
-      </c>
-      <c r="C55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>147674</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>201370</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>188048</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>181246</v>
       </c>
+      <c r="F55" s="17" t="n">
+        <v>180863</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="15" t="inlineStr">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="n"/>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B57" s="16" t="n">
-        <v>384474</v>
-      </c>
-      <c r="C57" s="16" t="n">
+      <c r="B57" s="17" t="n">
         <v>514809</v>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>425635</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>342875</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="E57" s="17" t="n">
         <v>455081</v>
       </c>
+      <c r="F57" s="17" t="n">
+        <v>375550</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n">
-        <v>633969</v>
-      </c>
-      <c r="C58" s="16" t="n">
+      <c r="B58" s="17" t="n">
         <v>740914</v>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>425635</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>342875</v>
       </c>
-      <c r="F58" s="16" t="n">
+      <c r="E58" s="17" t="n">
         <v>850784</v>
       </c>
+      <c r="F58" s="17" t="n">
+        <v>808500</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B59" s="16" t="n">
-        <v>1320756</v>
-      </c>
-      <c r="C59" s="16" t="n">
+      <c r="B59" s="17" t="n">
         <v>1419084</v>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>1574799</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>1479976</v>
       </c>
-      <c r="F59" s="16" t="n">
+      <c r="E59" s="17" t="n">
         <v>1491472</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>1372343</v>
       </c>
     </row>
   </sheetData>
@@ -6452,6 +6583,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.EUR)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>184839</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>-43096</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>127541</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>55230</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>60231</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-89835</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-75715</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-43278</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-38331</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-23320</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-36363</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>103320</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-85740</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-6455</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-40307</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6482,13 +6735,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7202,7 +7455,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7320,7 +7573,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7496,7 +7749,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7674,13 +7927,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7719,27 +7972,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7765,11 +8018,9 @@
         </is>
       </c>
       <c r="D3" s="35" t="n">
-        <v>125970</v>
-      </c>
-      <c r="E3" s="35" t="n">
         <v>30586</v>
       </c>
+      <c r="E3" s="35" t="n"/>
       <c r="F3" s="35" t="n"/>
       <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n"/>
@@ -7798,9 +8049,11 @@
       <c r="D4" s="38" t="n"/>
       <c r="E4" s="38" t="n"/>
       <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
+      <c r="G4" s="38" t="n">
+        <v>486398</v>
+      </c>
       <c r="H4" s="38" t="n">
-        <v>486398</v>
+        <v>485502</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7827,9 +8080,11 @@
       <c r="D5" s="35" t="n"/>
       <c r="E5" s="35" t="n"/>
       <c r="F5" s="35" t="n"/>
-      <c r="G5" s="35" t="n"/>
+      <c r="G5" s="35" t="n">
+        <v>2145</v>
+      </c>
       <c r="H5" s="35" t="n">
-        <v>2145</v>
+        <v>0</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -7856,10 +8111,10 @@
       <c r="D6" s="38" t="n"/>
       <c r="E6" s="38" t="n"/>
       <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="38" t="n">
+      <c r="G6" s="38" t="n">
         <v>2</v>
       </c>
+      <c r="H6" s="38" t="n"/>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7883,19 +8138,19 @@
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>170</v>
+        <v>74</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
@@ -7919,13 +8174,13 @@
           <t>fsa:IncomeFromInvestmentsInParticipatingInterests</t>
         </is>
       </c>
-      <c r="D8" s="38" t="n"/>
+      <c r="D8" s="38" t="n">
+        <v>-32968</v>
+      </c>
       <c r="E8" s="38" t="n">
-        <v>-32968</v>
-      </c>
-      <c r="F8" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="38" t="n"/>
       <c r="G8" s="38" t="n"/>
       <c r="H8" s="38" t="n"/>
       <c r="I8" s="39" t="inlineStr">
@@ -7951,12 +8206,14 @@
         </is>
       </c>
       <c r="D9" s="35" t="n"/>
-      <c r="E9" s="35" t="n"/>
-      <c r="F9" s="35" t="n">
+      <c r="E9" s="35" t="n">
         <v>-529</v>
       </c>
+      <c r="F9" s="35" t="n"/>
       <c r="G9" s="35" t="n"/>
-      <c r="H9" s="35" t="n"/>
+      <c r="H9" s="35" t="n">
+        <v>215</v>
+      </c>
       <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7982,10 +8239,10 @@
       <c r="D10" s="38" t="n"/>
       <c r="E10" s="38" t="n"/>
       <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n">
+      <c r="G10" s="38" t="n">
         <v>-2891</v>
       </c>
+      <c r="H10" s="38" t="n"/>
       <c r="I10" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -8009,10 +8266,10 @@
         </is>
       </c>
       <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n">
+      <c r="E11" s="35" t="n">
         <v>13</v>
       </c>
+      <c r="F11" s="35" t="n"/>
       <c r="G11" s="35" t="n"/>
       <c r="H11" s="35" t="n"/>
       <c r="I11" s="36" t="inlineStr">
@@ -8039,10 +8296,10 @@
       </c>
       <c r="D12" s="38" t="n"/>
       <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
-      <c r="G12" s="38" t="n">
+      <c r="F12" s="38" t="n">
         <v>-3160</v>
       </c>
+      <c r="G12" s="38" t="n"/>
       <c r="H12" s="38" t="n"/>
       <c r="I12" s="39" t="inlineStr">
         <is>
@@ -8066,13 +8323,13 @@
           <t>fsa:LongtermParticipatingInterests</t>
         </is>
       </c>
-      <c r="D13" s="35" t="n"/>
+      <c r="D13" s="35" t="n">
+        <v>32032</v>
+      </c>
       <c r="E13" s="35" t="n">
-        <v>32032</v>
-      </c>
-      <c r="F13" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="F13" s="35" t="n"/>
       <c r="G13" s="35" t="n"/>
       <c r="H13" s="35" t="n"/>
       <c r="I13" s="36" t="inlineStr">
@@ -8100,7 +8357,9 @@
       <c r="D14" s="38" t="n"/>
       <c r="E14" s="38" t="n"/>
       <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
+      <c r="G14" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="H14" s="38" t="n">
         <v>0</v>
       </c>
@@ -8126,13 +8385,13 @@
           <t>fsa:LongtermReceivablesFromAssociates</t>
         </is>
       </c>
-      <c r="D15" s="35" t="n"/>
+      <c r="D15" s="35" t="n">
+        <v>24052</v>
+      </c>
       <c r="E15" s="35" t="n">
-        <v>24052</v>
-      </c>
-      <c r="F15" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="F15" s="35" t="n"/>
       <c r="G15" s="35" t="n"/>
       <c r="H15" s="35" t="n"/>
       <c r="I15" s="36" t="inlineStr">
@@ -8158,19 +8417,19 @@
         </is>
       </c>
       <c r="D16" s="38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" s="38" t="n">
+        <v>23</v>
+      </c>
+      <c r="G16" s="38" t="n">
         <v>22</v>
       </c>
-      <c r="F16" s="38" t="n">
-        <v>24</v>
-      </c>
-      <c r="G16" s="38" t="n">
-        <v>23</v>
-      </c>
       <c r="H16" s="38" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I16" s="39" t="inlineStr">
         <is>
@@ -8196,10 +8455,10 @@
       </c>
       <c r="D17" s="35" t="n"/>
       <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n">
+      <c r="F17" s="35" t="n">
         <v>50000</v>
       </c>
+      <c r="G17" s="35" t="n"/>
       <c r="H17" s="35" t="n"/>
       <c r="I17" s="36" t="inlineStr">
         <is>
@@ -8224,10 +8483,10 @@
         </is>
       </c>
       <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n">
+      <c r="E18" s="38" t="n">
         <v>21922</v>
       </c>
+      <c r="F18" s="38" t="n"/>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
       <c r="I18" s="39" t="inlineStr">
@@ -8253,11 +8512,9 @@
         </is>
       </c>
       <c r="D19" s="35" t="n">
-        <v>250</v>
-      </c>
-      <c r="E19" s="35" t="n">
         <v>0</v>
       </c>
+      <c r="E19" s="35" t="n"/>
       <c r="F19" s="35" t="n"/>
       <c r="G19" s="35" t="n"/>
       <c r="H19" s="35" t="n"/>
@@ -8286,9 +8543,7 @@
       <c r="D20" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="38" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" s="38" t="n"/>
       <c r="F20" s="38" t="n"/>
       <c r="G20" s="38" t="n"/>
       <c r="H20" s="38" t="n"/>
@@ -8317,9 +8572,11 @@
       <c r="D21" s="35" t="n"/>
       <c r="E21" s="35" t="n"/>
       <c r="F21" s="35" t="n"/>
-      <c r="G21" s="35" t="n"/>
+      <c r="G21" s="35" t="n">
+        <v>-205</v>
+      </c>
       <c r="H21" s="35" t="n">
-        <v>-205</v>
+        <v>-5494</v>
       </c>
       <c r="I21" s="36" t="inlineStr">
         <is>
@@ -8344,17 +8601,15 @@
         </is>
       </c>
       <c r="D22" s="38" t="n">
-        <v>52238</v>
+        <v>76515</v>
       </c>
       <c r="E22" s="38" t="n">
-        <v>76515</v>
+        <v>31679</v>
       </c>
       <c r="F22" s="38" t="n">
-        <v>31679</v>
-      </c>
-      <c r="G22" s="38" t="n">
         <v>16887</v>
       </c>
+      <c r="G22" s="38" t="n"/>
       <c r="H22" s="38" t="n"/>
       <c r="I22" s="39" t="inlineStr">
         <is>
@@ -8381,9 +8636,11 @@
       <c r="D23" s="35" t="n"/>
       <c r="E23" s="35" t="n"/>
       <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
+      <c r="G23" s="35" t="n">
+        <v>15353</v>
+      </c>
       <c r="H23" s="35" t="n">
-        <v>15353</v>
+        <v>163</v>
       </c>
       <c r="I23" s="36" t="inlineStr">
         <is>
@@ -8410,9 +8667,11 @@
       <c r="D24" s="38" t="n"/>
       <c r="E24" s="38" t="n"/>
       <c r="F24" s="38" t="n"/>
-      <c r="G24" s="38" t="n"/>
+      <c r="G24" s="38" t="n">
+        <v>195</v>
+      </c>
       <c r="H24" s="38" t="n">
-        <v>195</v>
+        <v>656</v>
       </c>
       <c r="I24" s="39" t="inlineStr">
         <is>
@@ -8428,12 +8687,12 @@
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+          <t>fsa:TransferredToFromMinorityInterests</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
+          <t>fsa:TransferredToFromMinorityInterests</t>
         </is>
       </c>
       <c r="D25" s="35" t="n"/>
@@ -8441,7 +8700,7 @@
       <c r="F25" s="35" t="n"/>
       <c r="G25" s="35" t="n"/>
       <c r="H25" s="35" t="n">
-        <v>-16560</v>
+        <v>7125</v>
       </c>
       <c r="I25" s="36" t="inlineStr">
         <is>
@@ -8457,22 +8716,51 @@
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
+          <t>fsa:TransferredToFromOtherStatutoryReserves</t>
         </is>
       </c>
       <c r="D26" s="38" t="n"/>
       <c r="E26" s="38" t="n"/>
       <c r="F26" s="38" t="n"/>
       <c r="G26" s="38" t="n">
-        <v>66779</v>
+        <v>-16560</v>
       </c>
       <c r="H26" s="38" t="n"/>
       <c r="I26" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="inlineStr">
+        <is>
+          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>fsa:TransferredToReserveForEntrepreneurialCompany</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="n"/>
+      <c r="E27" s="35" t="n"/>
+      <c r="F27" s="35" t="n">
+        <v>66779</v>
+      </c>
+      <c r="G27" s="35" t="n"/>
+      <c r="H27" s="35" t="n"/>
+      <c r="I27" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
